--- a/backend/Location.xlsx
+++ b/backend/Location.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Coding\Projects\Metro_React JS\backend\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Coding\Projects\Ahmedabad Metro\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B923E5-E1C4-47FF-AD16-A79449AB655D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E868D4-B3F8-47A2-8101-9C3B7CCB7266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F605D172-C8CF-4215-BA16-067A9175F1B0}"/>
   </bookViews>
@@ -165,9 +165,6 @@
     <t>Sector-1</t>
   </si>
   <si>
-    <t>Sector 10A</t>
-  </si>
-  <si>
     <t>Sachivalaya</t>
   </si>
   <si>
@@ -220,6 +217,9 @@
   </si>
   <si>
     <t>Corridor-2</t>
+  </si>
+  <si>
+    <t>Sector-10A</t>
   </si>
 </sst>
 </file>
@@ -579,19 +579,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70162A79-1230-4432-BE6E-D208A479A384}">
   <dimension ref="A1:D57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="3" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" t="s">
-        <v>54</v>
-      </c>
       <c r="D1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -605,7 +608,7 @@
         <v>72.667604842000699</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -619,7 +622,7 @@
         <v>72.658935016270405</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -633,7 +636,7 @@
         <v>72.665694809466103</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -647,7 +650,7 @@
         <v>72.635484124808798</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -661,7 +664,7 @@
         <v>72.628743495973197</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -675,7 +678,7 @@
         <v>72.617493153644702</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -689,12 +692,12 @@
         <v>72.607025182480299</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B9">
         <v>23.024935329092699</v>
@@ -703,12 +706,12 @@
         <v>72.602925401795403</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B10">
         <v>23.0289456808026</v>
@@ -717,7 +720,7 @@
         <v>72.587233143261898</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -731,7 +734,7 @@
         <v>72.581499995973999</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -745,7 +748,7 @@
         <v>72.567010809467106</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -759,7 +762,7 @@
         <v>72.561684422960198</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -773,7 +776,7 @@
         <v>72.553021595974101</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -787,7 +790,7 @@
         <v>72.543395153645406</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -801,7 +804,7 @@
         <v>72.535146155494999</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -815,7 +818,7 @@
         <v>72.524888553645496</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -829,7 +832,7 @@
         <v>72.516708538303007</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -843,7 +846,7 @@
         <v>72.505558649075198</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -857,7 +860,7 @@
         <v>72.5375285113155</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -871,7 +874,7 @@
         <v>72.533449822959298</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -885,7 +888,7 @@
         <v>72.537161753644696</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -899,7 +902,7 @@
         <v>72.548700555494094</v>
       </c>
       <c r="D23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -913,7 +916,7 @@
         <v>72.562369153644894</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -927,7 +930,7 @@
         <v>72.569002253644896</v>
       </c>
       <c r="D25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -941,7 +944,7 @@
         <v>72.567042995974006</v>
       </c>
       <c r="D26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -955,7 +958,7 @@
         <v>72.565162575799505</v>
       </c>
       <c r="D27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -969,7 +972,7 @@
         <v>72.562354653645698</v>
       </c>
       <c r="D28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -983,7 +986,7 @@
         <v>72.565811695974702</v>
       </c>
       <c r="D29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -997,7 +1000,7 @@
         <v>72.574765253646106</v>
       </c>
       <c r="D30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -1011,7 +1014,7 @@
         <v>72.586398055495494</v>
       </c>
       <c r="D31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -1025,7 +1028,7 @@
         <v>72.5932681383036</v>
       </c>
       <c r="D32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1039,7 +1042,7 @@
         <v>72.592218440153403</v>
       </c>
       <c r="D33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1053,7 +1056,7 @@
         <v>72.596794911318</v>
       </c>
       <c r="D34" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -1061,13 +1064,13 @@
         <v>30</v>
       </c>
       <c r="B35">
-        <v>23.105704238531001</v>
+        <v>23.106267628570301</v>
       </c>
       <c r="C35">
-        <v>72.603306011263001</v>
+        <v>72.603369978503494</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -1081,7 +1084,7 @@
         <v>72.608994324811505</v>
       </c>
       <c r="D36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -1095,7 +1098,7 @@
         <v>72.615647858621202</v>
       </c>
       <c r="D37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -1109,7 +1112,7 @@
         <v>72.622139495976199</v>
       </c>
       <c r="D38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -1123,7 +1126,7 @@
         <v>72.631278707619899</v>
       </c>
       <c r="D39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -1131,13 +1134,13 @@
         <v>35</v>
       </c>
       <c r="B40">
-        <v>23.145787360021298</v>
+        <v>23.141999445118401</v>
       </c>
       <c r="C40">
-        <v>72.638109268058898</v>
+        <v>72.638426355820698</v>
       </c>
       <c r="D40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -1151,7 +1154,7 @@
         <v>72.643465318146895</v>
       </c>
       <c r="D41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -1165,7 +1168,7 @@
         <v>72.647701526661905</v>
       </c>
       <c r="D42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -1179,7 +1182,7 @@
         <v>72.648305451799004</v>
       </c>
       <c r="D43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -1193,7 +1196,7 @@
         <v>72.647278809470606</v>
       </c>
       <c r="D44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -1207,7 +1210,7 @@
         <v>72.643523640155806</v>
       </c>
       <c r="D45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -1221,7 +1224,7 @@
         <v>72.639789726662997</v>
       </c>
       <c r="D46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1235,105 +1238,105 @@
         <v>72.643460638306905</v>
       </c>
       <c r="D47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="B48">
-        <v>23.212847938945899</v>
+        <v>23.211124769155798</v>
       </c>
       <c r="C48">
-        <v>72.651875701083398</v>
+        <v>72.651006791999293</v>
       </c>
       <c r="D48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B49">
-        <v>23.2151</v>
+        <v>23.215084918900502</v>
       </c>
       <c r="C49">
-        <v>72.659099999999995</v>
+        <v>72.658768030625794</v>
       </c>
       <c r="D49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B50">
-        <v>23.233792589420599</v>
+        <v>23.224204879834701</v>
       </c>
       <c r="C50">
-        <v>72.6725741380302</v>
+        <v>72.6642396728584</v>
       </c>
       <c r="D50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B51">
-        <v>23.227315601245799</v>
+        <v>23.2292945570962</v>
       </c>
       <c r="C51">
-        <v>72.659816795978699</v>
+        <v>72.659416699988199</v>
       </c>
       <c r="D51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52">
-        <v>23.231214815542099</v>
+        <v>23.234030869944</v>
       </c>
       <c r="C52">
-        <v>72.644017793972296</v>
+        <v>72.650200372920807</v>
       </c>
       <c r="D52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B53">
-        <v>23.248731945333901</v>
+        <v>23.2399706390561</v>
       </c>
       <c r="C53">
-        <v>72.6428810700708</v>
+        <v>72.641329092269601</v>
       </c>
       <c r="D53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B54">
-        <v>23.233927425215299</v>
+        <v>23.237442198075001</v>
       </c>
       <c r="C54">
-        <v>72.6334249959788</v>
+        <v>72.634831665421999</v>
       </c>
       <c r="D54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -1347,12 +1350,12 @@
         <v>72.647669318148303</v>
       </c>
       <c r="D55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B56">
         <v>23.1551346994694</v>
@@ -1361,12 +1364,12 @@
         <v>72.663091095976895</v>
       </c>
       <c r="D56" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B57">
         <v>23.153534590230802</v>
@@ -1375,7 +1378,7 @@
         <v>72.685469122963099</v>
       </c>
       <c r="D57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
